--- a/sample_annots/figures/TableS1.xlsx
+++ b/sample_annots/figures/TableS1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="336">
   <si>
     <t xml:space="preserve">sampleId</t>
   </si>
@@ -47,6 +47,21 @@
     <t xml:space="preserve">log10frags_cutoff</t>
   </si>
   <si>
+    <t xml:space="preserve">n_cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_TSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_TSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_fragments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_fragments</t>
+  </si>
+  <si>
     <t xml:space="preserve">C19_mod_055</t>
   </si>
   <si>
@@ -329,10 +344,10 @@
     <t xml:space="preserve">Influenza_d30_flu01_4</t>
   </si>
   <si>
-    <t xml:space="preserve">Influenza_d30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">day30</t>
+    <t xml:space="preserve">Influenza_d28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">day28</t>
   </si>
   <si>
     <t xml:space="preserve">flu01_4</t>
@@ -1367,34 +1382,49 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J2" t="n">
         <v>7</v>
@@ -1402,34 +1432,49 @@
       <c r="K2" t="n">
         <v>3.7</v>
       </c>
+      <c r="L2" t="n">
+        <v>490</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.98517755102041</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9.6665</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.97578234057055</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.96001845907444</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
         <v>7</v>
@@ -1437,34 +1482,49 @@
       <c r="K3" t="n">
         <v>3.5</v>
       </c>
+      <c r="L3" t="n">
+        <v>219</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9.5005296803653</v>
+      </c>
+      <c r="N3" t="n">
+        <v>9.331</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.76370569385995</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.76072397214195</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J4" t="n">
         <v>7</v>
@@ -1472,34 +1532,49 @@
       <c r="K4" t="n">
         <v>3.8</v>
       </c>
+      <c r="L4" t="n">
+        <v>558</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.2206702508961</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10.029</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.06567941935561</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.04571401495975</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J5" t="n">
         <v>8</v>
@@ -1507,34 +1582,49 @@
       <c r="K5" t="n">
         <v>3.7</v>
       </c>
+      <c r="L5" t="n">
+        <v>1403</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11.0192081254455</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10.844</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.87548804462076</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.84466352824024</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
         <v>7</v>
@@ -1542,34 +1632,49 @@
       <c r="K6" t="n">
         <v>3.6</v>
       </c>
+      <c r="L6" t="n">
+        <v>2070</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10.2509855072464</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.88014080485203</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.86442207615439</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
@@ -1577,34 +1682,49 @@
       <c r="K7" t="n">
         <v>3.8</v>
       </c>
+      <c r="L7" t="n">
+        <v>1212</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.78846204620462</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.5315</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.95241758879517</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.93074532532392</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J8" t="n">
         <v>8</v>
@@ -1612,34 +1732,49 @@
       <c r="K8" t="n">
         <v>3.5</v>
       </c>
+      <c r="L8" t="n">
+        <v>1707</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11.4747662565905</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11.275</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.83604192330277</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.82477646247555</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
         <v>46</v>
       </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" t="s">
-        <v>41</v>
-      </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J9" t="n">
         <v>6</v>
@@ -1647,34 +1782,49 @@
       <c r="K9" t="n">
         <v>3.5</v>
       </c>
+      <c r="L9" t="n">
+        <v>844</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9.30252369668246</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.0225</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.82489897031978</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.8168043701686</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
         <v>8</v>
@@ -1682,34 +1832,49 @@
       <c r="K10" t="n">
         <v>3.2</v>
       </c>
+      <c r="L10" t="n">
+        <v>2857</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12.9479478473924</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12.924</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.60060587546703</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.58058287681437</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J11" t="n">
         <v>7</v>
@@ -1717,34 +1882,49 @@
       <c r="K11" t="n">
         <v>3.2</v>
       </c>
+      <c r="L11" t="n">
+        <v>901</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11.3098534961154</v>
+      </c>
+      <c r="N11" t="n">
+        <v>11.018</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.52908831461723</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.5210072524086</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J12" t="n">
         <v>5</v>
@@ -1752,34 +1932,49 @@
       <c r="K12" t="n">
         <v>3.5</v>
       </c>
+      <c r="L12" t="n">
+        <v>253</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9.05466007905138</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8.832</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.76965883619943</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.75815462196739</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J13" t="n">
         <v>6</v>
@@ -1787,34 +1982,49 @@
       <c r="K13" t="n">
         <v>3.7</v>
       </c>
+      <c r="L13" t="n">
+        <v>676</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9.57711982248521</v>
+      </c>
+      <c r="N13" t="n">
+        <v>9.3005</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.95011809703878</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.91879019175658</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
         <v>6</v>
@@ -1822,34 +2032,49 @@
       <c r="K14" t="n">
         <v>3.5</v>
       </c>
+      <c r="L14" t="n">
+        <v>94</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8.895</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8.7085</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.66571403846755</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.63918751418068</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
         <v>7</v>
@@ -1857,34 +2082,49 @@
       <c r="K15" t="n">
         <v>3.8</v>
       </c>
+      <c r="L15" t="n">
+        <v>367</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10.4481226158038</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10.225</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.1074509336541</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.06985302111362</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
         <v>8</v>
@@ -1892,34 +2132,49 @@
       <c r="K16" t="n">
         <v>3.6</v>
       </c>
+      <c r="L16" t="n">
+        <v>2774</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11.5309174477289</v>
+      </c>
+      <c r="N16" t="n">
+        <v>11.4475</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.94426513543467</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.92218028269078</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
         <v>8</v>
@@ -1927,34 +2182,49 @@
       <c r="K17" t="n">
         <v>3.6</v>
       </c>
+      <c r="L17" t="n">
+        <v>2267</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11.1353220114689</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11.047</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.96175329901996</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.94650139056959</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
         <v>6</v>
@@ -1962,34 +2232,49 @@
       <c r="K18" t="n">
         <v>3.7</v>
       </c>
+      <c r="L18" t="n">
+        <v>1530</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9.82533790849673</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.568</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.0518130664778</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.03786451017433</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
         <v>8</v>
@@ -1997,34 +2282,49 @@
       <c r="K19" t="n">
         <v>3.8</v>
       </c>
+      <c r="L19" t="n">
+        <v>422</v>
+      </c>
+      <c r="M19" t="n">
+        <v>9.70245260663507</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.4625</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.97304676988384</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.93076966064304</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
         <v>6</v>
@@ -2032,34 +2332,49 @@
       <c r="K20" t="n">
         <v>3.8</v>
       </c>
+      <c r="L20" t="n">
+        <v>961</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10.2808772112383</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10.006</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.1456349636804</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4.13893394025692</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" t="s">
         <v>86</v>
       </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>81</v>
-      </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G21" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
         <v>8</v>
@@ -2067,34 +2382,49 @@
       <c r="K21" t="n">
         <v>3.4</v>
       </c>
+      <c r="L21" t="n">
+        <v>5475</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11.3783052054795</v>
+      </c>
+      <c r="N21" t="n">
+        <v>11.154</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.81348327510009</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.80023578932735</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22" t="s">
         <v>96</v>
       </c>
-      <c r="G22" t="s">
-        <v>97</v>
-      </c>
-      <c r="H22" t="s">
-        <v>91</v>
-      </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
         <v>9</v>
@@ -2102,34 +2432,49 @@
       <c r="K22" t="n">
         <v>3.5</v>
       </c>
+      <c r="L22" t="n">
+        <v>5189</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12.529278280979</v>
+      </c>
+      <c r="N22" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.82928931876764</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.8055008581584</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G23" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H23" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
         <v>7</v>
@@ -2137,34 +2482,49 @@
       <c r="K23" t="n">
         <v>3.3</v>
       </c>
+      <c r="L23" t="n">
+        <v>1766</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9.45668289920725</v>
+      </c>
+      <c r="N23" t="n">
+        <v>9.055</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.74703333206107</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.74597213310568</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F24" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G24" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
         <v>8</v>
@@ -2172,34 +2532,49 @@
       <c r="K24" t="n">
         <v>3.4</v>
       </c>
+      <c r="L24" t="n">
+        <v>6914</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11.6547421174429</v>
+      </c>
+      <c r="N24" t="n">
+        <v>11.372</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.78488825837744</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3.76592920060786</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
         <v>86</v>
       </c>
-      <c r="C25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" t="s">
-        <v>81</v>
-      </c>
       <c r="E25" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
         <v>8</v>
@@ -2207,34 +2582,49 @@
       <c r="K25" t="n">
         <v>3.3</v>
       </c>
+      <c r="L25" t="n">
+        <v>7882</v>
+      </c>
+      <c r="M25" t="n">
+        <v>12.4634594011672</v>
+      </c>
+      <c r="N25" t="n">
+        <v>12.235</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.69337950086272</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.67361983633438</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F26" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H26" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
         <v>10</v>
@@ -2242,34 +2632,49 @@
       <c r="K26" t="n">
         <v>3.4</v>
       </c>
+      <c r="L26" t="n">
+        <v>6996</v>
+      </c>
+      <c r="M26" t="n">
+        <v>12.967660806175</v>
+      </c>
+      <c r="N26" t="n">
+        <v>12.663</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.77537915956224</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.75989436746457</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G27" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H27" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I27" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
         <v>9</v>
@@ -2277,34 +2682,49 @@
       <c r="K27" t="n">
         <v>3.4</v>
       </c>
+      <c r="L27" t="n">
+        <v>5797</v>
+      </c>
+      <c r="M27" t="n">
+        <v>12.5122270139727</v>
+      </c>
+      <c r="N27" t="n">
+        <v>12.243</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.76329000703999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.74554320199802</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F28" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G28" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H28" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
         <v>10</v>
@@ -2312,34 +2732,49 @@
       <c r="K28" t="n">
         <v>3.3</v>
       </c>
+      <c r="L28" t="n">
+        <v>6021</v>
+      </c>
+      <c r="M28" t="n">
+        <v>14.1440642750374</v>
+      </c>
+      <c r="N28" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.55474391851846</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.51917146382166</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" t="s">
         <v>86</v>
       </c>
-      <c r="C29" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" t="s">
-        <v>81</v>
-      </c>
       <c r="E29" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F29" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G29" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
         <v>10</v>
@@ -2347,34 +2782,49 @@
       <c r="K29" t="n">
         <v>3.8</v>
       </c>
+      <c r="L29" t="n">
+        <v>4559</v>
+      </c>
+      <c r="M29" t="n">
+        <v>12.5335906997148</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12.333</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.95626310165831</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.92890769024395</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E30" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F30" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H30" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
         <v>10</v>
@@ -2382,34 +2832,49 @@
       <c r="K30" t="n">
         <v>4</v>
       </c>
+      <c r="L30" t="n">
+        <v>1092</v>
+      </c>
+      <c r="M30" t="n">
+        <v>12.9552316849817</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12.834</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.17477318693154</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4.14871057594569</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G31" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
@@ -2417,34 +2882,49 @@
       <c r="K31" t="n">
         <v>3.7</v>
       </c>
+      <c r="L31" t="n">
+        <v>2768</v>
+      </c>
+      <c r="M31" t="n">
+        <v>13.0647536127168</v>
+      </c>
+      <c r="N31" t="n">
+        <v>12.8325</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.8935533322747</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.86320385902863</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F32" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I32" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
         <v>10</v>
@@ -2452,34 +2932,49 @@
       <c r="K32" t="n">
         <v>3.7</v>
       </c>
+      <c r="L32" t="n">
+        <v>7922</v>
+      </c>
+      <c r="M32" t="n">
+        <v>12.698469199697</v>
+      </c>
+      <c r="N32" t="n">
+        <v>12.413</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.89940147049056</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.86785034575198</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" t="s">
         <v>86</v>
       </c>
-      <c r="C33" t="s">
-        <v>87</v>
-      </c>
-      <c r="D33" t="s">
-        <v>81</v>
-      </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F33" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G33" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
         <v>10</v>
@@ -2487,34 +2982,49 @@
       <c r="K33" t="n">
         <v>3.8</v>
       </c>
+      <c r="L33" t="n">
+        <v>5239</v>
+      </c>
+      <c r="M33" t="n">
+        <v>13.4304267990074</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13.376</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4.04228928133166</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4.02209829746114</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F34" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G34" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H34" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
         <v>10</v>
@@ -2522,34 +3032,49 @@
       <c r="K34" t="n">
         <v>3.8</v>
       </c>
+      <c r="L34" t="n">
+        <v>1655</v>
+      </c>
+      <c r="M34" t="n">
+        <v>13.6852549848943</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13.556</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4.04415169411748</v>
+      </c>
+      <c r="P34" t="n">
+        <v>4.03165079355126</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F35" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G35" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H35" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
         <v>10</v>
@@ -2557,34 +3082,49 @@
       <c r="K35" t="n">
         <v>3.8</v>
       </c>
+      <c r="L35" t="n">
+        <v>1850</v>
+      </c>
+      <c r="M35" t="n">
+        <v>12.5265908108108</v>
+      </c>
+      <c r="N35" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4.03275609243766</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4.01805522118583</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E36" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F36" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G36" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H36" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I36" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
         <v>10</v>
@@ -2592,34 +3132,49 @@
       <c r="K36" t="n">
         <v>3.8</v>
       </c>
+      <c r="L36" t="n">
+        <v>2887</v>
+      </c>
+      <c r="M36" t="n">
+        <v>12.796058538275</v>
+      </c>
+      <c r="N36" t="n">
+        <v>12.585</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4.0028311152304</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.97863694838447</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" t="s">
         <v>86</v>
       </c>
-      <c r="C37" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" t="s">
-        <v>81</v>
-      </c>
       <c r="E37" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F37" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G37" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
         <v>10</v>
@@ -2627,34 +3182,49 @@
       <c r="K37" t="n">
         <v>3.8</v>
       </c>
+      <c r="L37" t="n">
+        <v>1381</v>
+      </c>
+      <c r="M37" t="n">
+        <v>13.969905865315</v>
+      </c>
+      <c r="N37" t="n">
+        <v>14.042</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4.17545339025019</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4.16357876518877</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E38" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F38" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G38" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H38" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I38" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
         <v>10</v>
@@ -2662,34 +3232,49 @@
       <c r="K38" t="n">
         <v>3.7</v>
       </c>
+      <c r="L38" t="n">
+        <v>6053</v>
+      </c>
+      <c r="M38" t="n">
+        <v>13.3130160251115</v>
+      </c>
+      <c r="N38" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.95968523598812</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3.94156112023607</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D39" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F39" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G39" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H39" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
         <v>8</v>
@@ -2697,34 +3282,49 @@
       <c r="K39" t="n">
         <v>3.8</v>
       </c>
+      <c r="L39" t="n">
+        <v>1823</v>
+      </c>
+      <c r="M39" t="n">
+        <v>11.6647372462973</v>
+      </c>
+      <c r="N39" t="n">
+        <v>11.506</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4.15592601094869</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4.14407580619855</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E40" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F40" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G40" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H40" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I40" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
         <v>8</v>
@@ -2732,34 +3332,49 @@
       <c r="K40" t="n">
         <v>3.8</v>
       </c>
+      <c r="L40" t="n">
+        <v>3338</v>
+      </c>
+      <c r="M40" t="n">
+        <v>12.4921929298981</v>
+      </c>
+      <c r="N40" t="n">
+        <v>12.4645</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4.00867416427378</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3.98000336206001</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F41" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G41" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I41" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
         <v>7</v>
@@ -2767,34 +3382,49 @@
       <c r="K41" t="n">
         <v>3.3</v>
       </c>
+      <c r="L41" t="n">
+        <v>6001</v>
+      </c>
+      <c r="M41" t="n">
+        <v>9.92747658723546</v>
+      </c>
+      <c r="N41" t="n">
+        <v>9.564</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.65854675087562</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3.65715150190097</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E42" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F42" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G42" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
         <v>10</v>
@@ -2802,34 +3432,49 @@
       <c r="K42" t="n">
         <v>3.8</v>
       </c>
+      <c r="L42" t="n">
+        <v>1024</v>
+      </c>
+      <c r="M42" t="n">
+        <v>12.4279306640625</v>
+      </c>
+      <c r="N42" t="n">
+        <v>12.177</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.94026162630321</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3.91905186543238</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E43" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F43" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G43" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I43" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
         <v>10</v>
@@ -2837,34 +3482,49 @@
       <c r="K43" t="n">
         <v>3.5</v>
       </c>
+      <c r="L43" t="n">
+        <v>6582</v>
+      </c>
+      <c r="M43" t="n">
+        <v>14.1880132178669</v>
+      </c>
+      <c r="N43" t="n">
+        <v>14.0535</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.79343587121649</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.78866320737403</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E44" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F44" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G44" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I44" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
         <v>8</v>
@@ -2872,34 +3532,49 @@
       <c r="K44" t="n">
         <v>3.3</v>
       </c>
+      <c r="L44" t="n">
+        <v>6087</v>
+      </c>
+      <c r="M44" t="n">
+        <v>11.2741808772794</v>
+      </c>
+      <c r="N44" t="n">
+        <v>10.983</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.58556927890373</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3.5643109099606</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E45" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F45" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="G45" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
         <v>10</v>
@@ -2907,34 +3582,49 @@
       <c r="K45" t="n">
         <v>3.6</v>
       </c>
+      <c r="L45" t="n">
+        <v>632</v>
+      </c>
+      <c r="M45" t="n">
+        <v>15.900878164557</v>
+      </c>
+      <c r="N45" t="n">
+        <v>15.9465</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3.79546086920672</v>
+      </c>
+      <c r="P45" t="n">
+        <v>3.76789721131226</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E46" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F46" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G46" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I46" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
         <v>8</v>
@@ -2942,32 +3632,47 @@
       <c r="K46" t="n">
         <v>3.5</v>
       </c>
+      <c r="L46" t="n">
+        <v>4609</v>
+      </c>
+      <c r="M46" t="n">
+        <v>10.7893525710566</v>
+      </c>
+      <c r="N46" t="n">
+        <v>10.456</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.759971673745</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3.74826557266874</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B47" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C47" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D47" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E47" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F47" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G47"/>
       <c r="H47" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I47" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
         <v>10</v>
@@ -2975,32 +3680,47 @@
       <c r="K47" t="n">
         <v>3.7</v>
       </c>
+      <c r="L47" t="n">
+        <v>1912</v>
+      </c>
+      <c r="M47" t="n">
+        <v>15.9924419456067</v>
+      </c>
+      <c r="N47" t="n">
+        <v>16.0685</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4.24125294242652</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4.26054837263698</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E48" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F48" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G48"/>
       <c r="H48" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I48" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
         <v>10</v>
@@ -3008,32 +3728,47 @@
       <c r="K48" t="n">
         <v>3.8</v>
       </c>
+      <c r="L48" t="n">
+        <v>1390</v>
+      </c>
+      <c r="M48" t="n">
+        <v>17.8046330935252</v>
+      </c>
+      <c r="N48" t="n">
+        <v>17.9845</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4.28990253581669</v>
+      </c>
+      <c r="P48" t="n">
+        <v>4.30558776805043</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B49" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C49" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E49" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F49" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G49"/>
       <c r="H49" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J49" t="n">
         <v>10</v>
@@ -3041,32 +3776,47 @@
       <c r="K49" t="n">
         <v>3.6</v>
       </c>
+      <c r="L49" t="n">
+        <v>2873</v>
+      </c>
+      <c r="M49" t="n">
+        <v>15.6987330316742</v>
+      </c>
+      <c r="N49" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4.17885795750835</v>
+      </c>
+      <c r="P49" t="n">
+        <v>4.20218851226605</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B50" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D50" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E50" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F50" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G50"/>
       <c r="H50" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I50" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
         <v>10</v>
@@ -3074,32 +3824,47 @@
       <c r="K50" t="n">
         <v>3.5</v>
       </c>
+      <c r="L50" t="n">
+        <v>4335</v>
+      </c>
+      <c r="M50" t="n">
+        <v>16.7272452133795</v>
+      </c>
+      <c r="N50" t="n">
+        <v>16.881</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.0543458841284</v>
+      </c>
+      <c r="P50" t="n">
+        <v>4.07503572592219</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B51" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C51" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E51" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F51" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G51"/>
       <c r="H51" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I51" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
         <v>10</v>
@@ -3107,32 +3872,47 @@
       <c r="K51" t="n">
         <v>3.7</v>
       </c>
+      <c r="L51" t="n">
+        <v>2953</v>
+      </c>
+      <c r="M51" t="n">
+        <v>16.5835912631222</v>
+      </c>
+      <c r="N51" t="n">
+        <v>16.857</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4.26130941030716</v>
+      </c>
+      <c r="P51" t="n">
+        <v>4.28253148381223</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B52" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C52" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E52" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F52" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G52"/>
       <c r="H52" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I52" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
         <v>10</v>
@@ -3140,32 +3920,47 @@
       <c r="K52" t="n">
         <v>3.7</v>
       </c>
+      <c r="L52" t="n">
+        <v>2650</v>
+      </c>
+      <c r="M52" t="n">
+        <v>15.271938490566</v>
+      </c>
+      <c r="N52" t="n">
+        <v>15.2685</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4.25129487957226</v>
+      </c>
+      <c r="P52" t="n">
+        <v>4.26875342487179</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B53" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C53" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E53" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F53" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G53"/>
       <c r="H53" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I53" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
         <v>10</v>
@@ -3173,32 +3968,47 @@
       <c r="K53" t="n">
         <v>3.7</v>
       </c>
+      <c r="L53" t="n">
+        <v>3913</v>
+      </c>
+      <c r="M53" t="n">
+        <v>16.15010350115</v>
+      </c>
+      <c r="N53" t="n">
+        <v>16.235</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4.10080048258816</v>
+      </c>
+      <c r="P53" t="n">
+        <v>4.10479428648628</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B54" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C54" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D54" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E54" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F54" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G54"/>
       <c r="H54" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I54" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
         <v>10</v>
@@ -3206,32 +4016,47 @@
       <c r="K54" t="n">
         <v>3.7</v>
       </c>
+      <c r="L54" t="n">
+        <v>3519</v>
+      </c>
+      <c r="M54" t="n">
+        <v>16.1972946859903</v>
+      </c>
+      <c r="N54" t="n">
+        <v>16.302</v>
+      </c>
+      <c r="O54" t="n">
+        <v>4.26700353245446</v>
+      </c>
+      <c r="P54" t="n">
+        <v>4.28818213061366</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B55" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C55" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D55" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E55" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F55" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G55"/>
       <c r="H55" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I55" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
         <v>10</v>
@@ -3239,32 +4064,47 @@
       <c r="K55" t="n">
         <v>3.5</v>
       </c>
+      <c r="L55" t="n">
+        <v>2860</v>
+      </c>
+      <c r="M55" t="n">
+        <v>16.0012797202797</v>
+      </c>
+      <c r="N55" t="n">
+        <v>16.2355</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4.18651192093791</v>
+      </c>
+      <c r="P55" t="n">
+        <v>4.20848164972046</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B56" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C56" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D56" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E56" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F56" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G56"/>
       <c r="H56" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I56" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
         <v>10</v>
@@ -3272,32 +4112,47 @@
       <c r="K56" t="n">
         <v>3.3</v>
       </c>
+      <c r="L56" t="n">
+        <v>3950</v>
+      </c>
+      <c r="M56" t="n">
+        <v>16.6293744303797</v>
+      </c>
+      <c r="N56" t="n">
+        <v>16.9075</v>
+      </c>
+      <c r="O56" t="n">
+        <v>4.11008673400887</v>
+      </c>
+      <c r="P56" t="n">
+        <v>4.13557784869273</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B57" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C57" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D57" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E57" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F57" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G57"/>
       <c r="H57" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I57" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
         <v>10</v>
@@ -3305,32 +4160,47 @@
       <c r="K57" t="n">
         <v>3.6</v>
       </c>
+      <c r="L57" t="n">
+        <v>4453</v>
+      </c>
+      <c r="M57" t="n">
+        <v>15.4264383561644</v>
+      </c>
+      <c r="N57" t="n">
+        <v>15.556</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4.15342281264232</v>
+      </c>
+      <c r="P57" t="n">
+        <v>4.16935109049242</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B58" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D58" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E58" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F58" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G58"/>
       <c r="H58" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I58" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
         <v>10</v>
@@ -3338,32 +4208,47 @@
       <c r="K58" t="n">
         <v>3.6</v>
       </c>
+      <c r="L58" t="n">
+        <v>3957</v>
+      </c>
+      <c r="M58" t="n">
+        <v>14.208417487996</v>
+      </c>
+      <c r="N58" t="n">
+        <v>14.081</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4.11475938416938</v>
+      </c>
+      <c r="P58" t="n">
+        <v>4.12784959018764</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B59" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C59" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D59" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E59" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F59" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G59"/>
       <c r="H59" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I59" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
         <v>10</v>
@@ -3371,32 +4256,47 @@
       <c r="K59" t="n">
         <v>3.6</v>
       </c>
+      <c r="L59" t="n">
+        <v>3590</v>
+      </c>
+      <c r="M59" t="n">
+        <v>15.660122005571</v>
+      </c>
+      <c r="N59" t="n">
+        <v>15.839</v>
+      </c>
+      <c r="O59" t="n">
+        <v>4.15275048130202</v>
+      </c>
+      <c r="P59" t="n">
+        <v>4.1732154059132</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B60" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C60" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D60" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E60" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F60" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G60"/>
       <c r="H60" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
         <v>10</v>
@@ -3404,32 +4304,47 @@
       <c r="K60" t="n">
         <v>3.8</v>
       </c>
+      <c r="L60" t="n">
+        <v>1959</v>
+      </c>
+      <c r="M60" t="n">
+        <v>16.5786442062277</v>
+      </c>
+      <c r="N60" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="O60" t="n">
+        <v>4.23981473925979</v>
+      </c>
+      <c r="P60" t="n">
+        <v>4.25604389870203</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C61" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D61" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E61" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F61" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G61"/>
       <c r="H61" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I61" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
         <v>10</v>
@@ -3437,32 +4352,47 @@
       <c r="K61" t="n">
         <v>3.5</v>
       </c>
+      <c r="L61" t="n">
+        <v>4995</v>
+      </c>
+      <c r="M61" t="n">
+        <v>15.7401315315315</v>
+      </c>
+      <c r="N61" t="n">
+        <v>15.878</v>
+      </c>
+      <c r="O61" t="n">
+        <v>4.08106042782979</v>
+      </c>
+      <c r="P61" t="n">
+        <v>4.10109376673666</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B62" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C62" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E62" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F62" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G62"/>
       <c r="H62" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I62" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
         <v>10</v>
@@ -3470,32 +4400,47 @@
       <c r="K62" t="n">
         <v>3.5</v>
       </c>
+      <c r="L62" t="n">
+        <v>3375</v>
+      </c>
+      <c r="M62" t="n">
+        <v>17.5748322962963</v>
+      </c>
+      <c r="N62" t="n">
+        <v>17.704</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4.12702149688115</v>
+      </c>
+      <c r="P62" t="n">
+        <v>4.1908077601319</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B63" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C63" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D63" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E63" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F63" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G63"/>
       <c r="H63" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I63" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
         <v>10</v>
@@ -3503,32 +4448,47 @@
       <c r="K63" t="n">
         <v>3.5</v>
       </c>
+      <c r="L63" t="n">
+        <v>3247</v>
+      </c>
+      <c r="M63" t="n">
+        <v>15.3364145364952</v>
+      </c>
+      <c r="N63" t="n">
+        <v>15.251</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4.05875784391057</v>
+      </c>
+      <c r="P63" t="n">
+        <v>4.07609404668248</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B64" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C64" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D64" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E64" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F64" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G64"/>
       <c r="H64" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I64" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
         <v>10</v>
@@ -3536,32 +4496,47 @@
       <c r="K64" t="n">
         <v>3.3</v>
       </c>
+      <c r="L64" t="n">
+        <v>6486</v>
+      </c>
+      <c r="M64" t="n">
+        <v>17.7351652790626</v>
+      </c>
+      <c r="N64" t="n">
+        <v>17.947</v>
+      </c>
+      <c r="O64" t="n">
+        <v>4.05377572430864</v>
+      </c>
+      <c r="P64" t="n">
+        <v>4.07901835469567</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B65" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D65" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E65" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F65" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G65"/>
       <c r="H65" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I65" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
         <v>10</v>
@@ -3569,32 +4544,47 @@
       <c r="K65" t="n">
         <v>3.5</v>
       </c>
+      <c r="L65" t="n">
+        <v>4557</v>
+      </c>
+      <c r="M65" t="n">
+        <v>16.3348472679394</v>
+      </c>
+      <c r="N65" t="n">
+        <v>16.349</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4.14407952735933</v>
+      </c>
+      <c r="P65" t="n">
+        <v>4.18500355649181</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B66" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C66" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D66" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E66" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F66" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G66"/>
       <c r="H66" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I66" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
         <v>10</v>
@@ -3602,32 +4592,47 @@
       <c r="K66" t="n">
         <v>3.5</v>
       </c>
+      <c r="L66" t="n">
+        <v>3149</v>
+      </c>
+      <c r="M66" t="n">
+        <v>17.1972572245157</v>
+      </c>
+      <c r="N66" t="n">
+        <v>17.365</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4.12806970006301</v>
+      </c>
+      <c r="P66" t="n">
+        <v>4.17866045853817</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B67" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C67" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D67" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E67" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F67" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G67"/>
       <c r="H67" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I67" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
         <v>8</v>
@@ -3635,32 +4640,47 @@
       <c r="K67" t="n">
         <v>3.5</v>
       </c>
+      <c r="L67" t="n">
+        <v>4356</v>
+      </c>
+      <c r="M67" t="n">
+        <v>14.1934162075298</v>
+      </c>
+      <c r="N67" t="n">
+        <v>14.1365</v>
+      </c>
+      <c r="O67" t="n">
+        <v>4.06674080873885</v>
+      </c>
+      <c r="P67" t="n">
+        <v>4.10568046294581</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B68" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C68" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D68" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E68" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F68" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G68"/>
       <c r="H68" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I68" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
         <v>10</v>
@@ -3668,32 +4688,47 @@
       <c r="K68" t="n">
         <v>3.8</v>
       </c>
+      <c r="L68" t="n">
+        <v>939</v>
+      </c>
+      <c r="M68" t="n">
+        <v>18.3362002129925</v>
+      </c>
+      <c r="N68" t="n">
+        <v>18.785</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4.3103916070761</v>
+      </c>
+      <c r="P68" t="n">
+        <v>4.3446280256941</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B69" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C69" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D69" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E69" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F69" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G69"/>
       <c r="H69" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I69" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
         <v>10</v>
@@ -3701,32 +4736,47 @@
       <c r="K69" t="n">
         <v>3.5</v>
       </c>
+      <c r="L69" t="n">
+        <v>3781</v>
+      </c>
+      <c r="M69" t="n">
+        <v>17.0254022745305</v>
+      </c>
+      <c r="N69" t="n">
+        <v>17.181</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4.04455394677394</v>
+      </c>
+      <c r="P69" t="n">
+        <v>4.06197994707488</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B70" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C70" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D70" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E70" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F70" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G70"/>
       <c r="H70" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I70" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
         <v>10</v>
@@ -3734,32 +4784,47 @@
       <c r="K70" t="n">
         <v>3.3</v>
       </c>
+      <c r="L70" t="n">
+        <v>3512</v>
+      </c>
+      <c r="M70" t="n">
+        <v>17.4458972095672</v>
+      </c>
+      <c r="N70" t="n">
+        <v>17.5445</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4.09209759822433</v>
+      </c>
+      <c r="P70" t="n">
+        <v>4.12656970053318</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B71" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C71" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D71" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E71" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F71" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G71"/>
       <c r="H71" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I71" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
         <v>10</v>
@@ -3767,32 +4832,47 @@
       <c r="K71" t="n">
         <v>3.5</v>
       </c>
+      <c r="L71" t="n">
+        <v>1360</v>
+      </c>
+      <c r="M71" t="n">
+        <v>14.2824014705882</v>
+      </c>
+      <c r="N71" t="n">
+        <v>13.846</v>
+      </c>
+      <c r="O71" t="n">
+        <v>4.06732241753316</v>
+      </c>
+      <c r="P71" t="n">
+        <v>4.08926909160663</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B72" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C72" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D72" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E72" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F72" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G72"/>
       <c r="H72" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I72" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
         <v>10</v>
@@ -3800,32 +4880,47 @@
       <c r="K72" t="n">
         <v>3.5</v>
       </c>
+      <c r="L72" t="n">
+        <v>3044</v>
+      </c>
+      <c r="M72" t="n">
+        <v>17.6023288436268</v>
+      </c>
+      <c r="N72" t="n">
+        <v>17.654</v>
+      </c>
+      <c r="O72" t="n">
+        <v>4.06132244278387</v>
+      </c>
+      <c r="P72" t="n">
+        <v>4.08436175266174</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B73" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C73" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D73" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E73" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F73" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G73"/>
       <c r="H73" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I73" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
         <v>10</v>
@@ -3833,32 +4928,47 @@
       <c r="K73" t="n">
         <v>3.5</v>
       </c>
+      <c r="L73" t="n">
+        <v>5963</v>
+      </c>
+      <c r="M73" t="n">
+        <v>17.4188435351333</v>
+      </c>
+      <c r="N73" t="n">
+        <v>17.681</v>
+      </c>
+      <c r="O73" t="n">
+        <v>3.99523489396422</v>
+      </c>
+      <c r="P73" t="n">
+        <v>4.00043407747932</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B74" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C74" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D74" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E74" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F74" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G74"/>
       <c r="H74" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I74" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
         <v>10</v>
@@ -3866,32 +4976,47 @@
       <c r="K74" t="n">
         <v>3.5</v>
       </c>
+      <c r="L74" t="n">
+        <v>2498</v>
+      </c>
+      <c r="M74" t="n">
+        <v>17.773917133707</v>
+      </c>
+      <c r="N74" t="n">
+        <v>18.0275</v>
+      </c>
+      <c r="O74" t="n">
+        <v>4.10229367451706</v>
+      </c>
+      <c r="P74" t="n">
+        <v>4.14024084064188</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B75" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C75" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D75" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E75" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F75" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G75"/>
       <c r="H75" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I75" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
         <v>10</v>
@@ -3899,32 +5024,47 @@
       <c r="K75" t="n">
         <v>3.5</v>
       </c>
+      <c r="L75" t="n">
+        <v>2185</v>
+      </c>
+      <c r="M75" t="n">
+        <v>17.0289455377574</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.144</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4.20286199796481</v>
+      </c>
+      <c r="P75" t="n">
+        <v>4.23696529910298</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B76" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C76" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D76" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E76" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F76" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G76"/>
       <c r="H76" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I76" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
         <v>10</v>
@@ -3932,32 +5072,47 @@
       <c r="K76" t="n">
         <v>3.5</v>
       </c>
+      <c r="L76" t="n">
+        <v>2699</v>
+      </c>
+      <c r="M76" t="n">
+        <v>16.3918266024453</v>
+      </c>
+      <c r="N76" t="n">
+        <v>16.579</v>
+      </c>
+      <c r="O76" t="n">
+        <v>4.20943811550106</v>
+      </c>
+      <c r="P76" t="n">
+        <v>4.23243700922055</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C77" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D77" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E77" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F77" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G77"/>
       <c r="H77" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I77" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
         <v>10</v>
@@ -3965,32 +5120,47 @@
       <c r="K77" t="n">
         <v>3.3</v>
       </c>
+      <c r="L77" t="n">
+        <v>7</v>
+      </c>
+      <c r="M77" t="n">
+        <v>17.6394285714286</v>
+      </c>
+      <c r="N77" t="n">
+        <v>16.615</v>
+      </c>
+      <c r="O77" t="n">
+        <v>4.26542481350386</v>
+      </c>
+      <c r="P77" t="n">
+        <v>4.28976727095278</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C78" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D78" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E78" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F78" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G78"/>
       <c r="H78" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I78" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
         <v>10</v>
@@ -3998,32 +5168,47 @@
       <c r="K78" t="n">
         <v>3.4</v>
       </c>
+      <c r="L78" t="n">
+        <v>4584</v>
+      </c>
+      <c r="M78" t="n">
+        <v>17.748905104712</v>
+      </c>
+      <c r="N78" t="n">
+        <v>17.839</v>
+      </c>
+      <c r="O78" t="n">
+        <v>4.05191080656177</v>
+      </c>
+      <c r="P78" t="n">
+        <v>4.0789821484028</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B79" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C79" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D79" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E79" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F79" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I79" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
         <v>10</v>
@@ -4031,32 +5216,47 @@
       <c r="K79" t="n">
         <v>3.6</v>
       </c>
+      <c r="L79" t="n">
+        <v>3917</v>
+      </c>
+      <c r="M79" t="n">
+        <v>15.6249841715599</v>
+      </c>
+      <c r="N79" t="n">
+        <v>15.685</v>
+      </c>
+      <c r="O79" t="n">
+        <v>4.17523922296776</v>
+      </c>
+      <c r="P79" t="n">
+        <v>4.20104189554268</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B80" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C80" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D80" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E80" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F80" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I80" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
         <v>10</v>
@@ -4064,32 +5264,47 @@
       <c r="K80" t="n">
         <v>3.8</v>
       </c>
+      <c r="L80" t="n">
+        <v>2656</v>
+      </c>
+      <c r="M80" t="n">
+        <v>15.536969126506</v>
+      </c>
+      <c r="N80" t="n">
+        <v>15.4565</v>
+      </c>
+      <c r="O80" t="n">
+        <v>4.03041798206777</v>
+      </c>
+      <c r="P80" t="n">
+        <v>4.01336396104752</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B81" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C81" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D81" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E81" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F81" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I81" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
         <v>10</v>
@@ -4097,32 +5312,47 @@
       <c r="K81" t="n">
         <v>3.5</v>
       </c>
+      <c r="L81" t="n">
+        <v>3372</v>
+      </c>
+      <c r="M81" t="n">
+        <v>16.0524537366548</v>
+      </c>
+      <c r="N81" t="n">
+        <v>16.102</v>
+      </c>
+      <c r="O81" t="n">
+        <v>4.06270507944978</v>
+      </c>
+      <c r="P81" t="n">
+        <v>4.08763946686228</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B82" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C82" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D82" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E82" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F82" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="G82"/>
       <c r="H82" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I82" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
         <v>10</v>
@@ -4130,32 +5360,47 @@
       <c r="K82" t="n">
         <v>3.6</v>
       </c>
+      <c r="L82" t="n">
+        <v>1116</v>
+      </c>
+      <c r="M82" t="n">
+        <v>17.0904256272401</v>
+      </c>
+      <c r="N82" t="n">
+        <v>17.2615</v>
+      </c>
+      <c r="O82" t="n">
+        <v>4.33989146442166</v>
+      </c>
+      <c r="P82" t="n">
+        <v>4.41889753105894</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>300</v>
+      </c>
+      <c r="B83" t="s">
         <v>295</v>
       </c>
-      <c r="B83" t="s">
-        <v>290</v>
-      </c>
       <c r="C83" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D83" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E83" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F83" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="G83"/>
       <c r="H83" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I83" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
         <v>10</v>
@@ -4163,32 +5408,47 @@
       <c r="K83" t="n">
         <v>3.4</v>
       </c>
+      <c r="L83" t="n">
+        <v>5097</v>
+      </c>
+      <c r="M83" t="n">
+        <v>17.5457333725721</v>
+      </c>
+      <c r="N83" t="n">
+        <v>17.912</v>
+      </c>
+      <c r="O83" t="n">
+        <v>4.01357971306706</v>
+      </c>
+      <c r="P83" t="n">
+        <v>4.03225602589045</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B84" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C84" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D84" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E84" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F84" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G84"/>
       <c r="H84" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I84" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
         <v>10</v>
@@ -4196,32 +5456,47 @@
       <c r="K84" t="n">
         <v>3.5</v>
       </c>
+      <c r="L84" t="n">
+        <v>1882</v>
+      </c>
+      <c r="M84" t="n">
+        <v>18.4821934112646</v>
+      </c>
+      <c r="N84" t="n">
+        <v>18.773</v>
+      </c>
+      <c r="O84" t="n">
+        <v>4.23703216389273</v>
+      </c>
+      <c r="P84" t="n">
+        <v>4.28189654965319</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B85" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C85" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D85" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E85" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F85" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="G85"/>
       <c r="H85" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I85" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
         <v>10</v>
@@ -4229,32 +5504,47 @@
       <c r="K85" t="n">
         <v>3.5</v>
       </c>
+      <c r="L85" t="n">
+        <v>588</v>
+      </c>
+      <c r="M85" t="n">
+        <v>19.2799710884354</v>
+      </c>
+      <c r="N85" t="n">
+        <v>19.656</v>
+      </c>
+      <c r="O85" t="n">
+        <v>4.03521892556869</v>
+      </c>
+      <c r="P85" t="n">
+        <v>4.0090622030793</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B86" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C86" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D86" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E86" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F86" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="G86"/>
       <c r="H86" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I86" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
         <v>10</v>
@@ -4262,32 +5552,47 @@
       <c r="K86" t="n">
         <v>3.8</v>
       </c>
+      <c r="L86" t="n">
+        <v>1608</v>
+      </c>
+      <c r="M86" t="n">
+        <v>16.3164539800995</v>
+      </c>
+      <c r="N86" t="n">
+        <v>16.6695</v>
+      </c>
+      <c r="O86" t="n">
+        <v>4.4560079943764</v>
+      </c>
+      <c r="P86" t="n">
+        <v>4.49177476802166</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C87" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D87" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E87" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F87" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G87"/>
       <c r="H87" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I87" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
         <v>10</v>
@@ -4295,32 +5600,47 @@
       <c r="K87" t="n">
         <v>3.8</v>
       </c>
+      <c r="L87" t="n">
+        <v>831</v>
+      </c>
+      <c r="M87" t="n">
+        <v>17.3065294825511</v>
+      </c>
+      <c r="N87" t="n">
+        <v>17.467</v>
+      </c>
+      <c r="O87" t="n">
+        <v>4.39406297903135</v>
+      </c>
+      <c r="P87" t="n">
+        <v>4.45327246144616</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B88" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C88" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D88" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E88" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F88" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G88"/>
       <c r="H88" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I88" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
         <v>10</v>
@@ -4328,32 +5648,47 @@
       <c r="K88" t="n">
         <v>3.5</v>
       </c>
+      <c r="L88" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M88" t="n">
+        <v>17.55916125</v>
+      </c>
+      <c r="N88" t="n">
+        <v>17.676</v>
+      </c>
+      <c r="O88" t="n">
+        <v>4.173840207905</v>
+      </c>
+      <c r="P88" t="n">
+        <v>4.23238613421669</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B89" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C89" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D89" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E89" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F89" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G89"/>
       <c r="H89" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I89" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J89" t="n">
         <v>10</v>
@@ -4361,32 +5696,47 @@
       <c r="K89" t="n">
         <v>3.5</v>
       </c>
+      <c r="L89" t="n">
+        <v>2587</v>
+      </c>
+      <c r="M89" t="n">
+        <v>16.6382736760727</v>
+      </c>
+      <c r="N89" t="n">
+        <v>16.835</v>
+      </c>
+      <c r="O89" t="n">
+        <v>4.25213449325252</v>
+      </c>
+      <c r="P89" t="n">
+        <v>4.31659930209386</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B90" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C90" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D90" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E90" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F90" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G90"/>
       <c r="H90" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I90" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J90" t="n">
         <v>10</v>
@@ -4394,32 +5744,47 @@
       <c r="K90" t="n">
         <v>3.6</v>
       </c>
+      <c r="L90" t="n">
+        <v>2831</v>
+      </c>
+      <c r="M90" t="n">
+        <v>16.8564065701166</v>
+      </c>
+      <c r="N90" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="O90" t="n">
+        <v>4.3379877850174</v>
+      </c>
+      <c r="P90" t="n">
+        <v>4.38255732190879</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B91" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C91" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D91" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E91" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F91" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G91"/>
       <c r="H91" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I91" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J91" t="n">
         <v>10</v>
@@ -4427,32 +5792,47 @@
       <c r="K91" t="n">
         <v>3.6</v>
       </c>
+      <c r="L91" t="n">
+        <v>2191</v>
+      </c>
+      <c r="M91" t="n">
+        <v>16.6766554084893</v>
+      </c>
+      <c r="N91" t="n">
+        <v>16.596</v>
+      </c>
+      <c r="O91" t="n">
+        <v>4.27830758050121</v>
+      </c>
+      <c r="P91" t="n">
+        <v>4.32750197254008</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B92" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C92" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D92" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E92" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="F92" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G92"/>
       <c r="H92" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I92" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J92" t="n">
         <v>10</v>
@@ -4460,38 +5840,68 @@
       <c r="K92" t="n">
         <v>3.6</v>
       </c>
+      <c r="L92" t="n">
+        <v>627</v>
+      </c>
+      <c r="M92" t="n">
+        <v>17.8054609250399</v>
+      </c>
+      <c r="N92" t="n">
+        <v>17.915</v>
+      </c>
+      <c r="O92" t="n">
+        <v>4.32307954545047</v>
+      </c>
+      <c r="P92" t="n">
+        <v>4.44105067674622</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B93" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C93" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D93" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E93" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F93" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="G93"/>
       <c r="H93" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I93" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J93" t="n">
         <v>10</v>
       </c>
       <c r="K93" t="n">
         <v>3.4</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1398</v>
+      </c>
+      <c r="M93" t="n">
+        <v>18.6834964234621</v>
+      </c>
+      <c r="N93" t="n">
+        <v>19.245</v>
+      </c>
+      <c r="O93" t="n">
+        <v>4.09878319546827</v>
+      </c>
+      <c r="P93" t="n">
+        <v>4.12337790096538</v>
       </c>
     </row>
   </sheetData>
